--- a/branches/feat/newborn-screening-valuesets/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/feat/newborn-screening-valuesets/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:48:20+00:00</t>
+    <t>2026-08-28T15:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/newborn-screening-valuesets/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
+++ b/branches/feat/newborn-screening-valuesets/StructureDefinition-mii-pr-seltene-therapieempfehlung-kombination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:01:21+00:00</t>
+    <t>2026-08-28T15:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
